--- a/01_DacTa_Spec/quanly_khohang_v0.xlsx
+++ b/01_DacTa_Spec/quanly_khohang_v0.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quy trình tiếp nhận, quản lý và kiểm toán 1 phiếu kho hàng điện máy gồm 6 hành vi: H1 tiếp nhận yêu cầu (chép mã phiếu vào bộ đệm stack), H2 tạo danh mục lô hàng (cấp phát mảng động các kiện hàng trên heap), H3 tính tổng tiền tồn kho (số nguyên 32-bit, VND), H4 nhận xác thực chữ ký thủ kho (chép token ủy quyền, phân quyền xuất kho), H5 ghi nhật ký kiểm kê kho (audit log), H6 đóng phiên kho hàng (worker nhập kho và worker xuất kho tự động dùng chung phiên). Bản v0 CÀI LỖI CÓ CHỦ ĐÍCH (18 trường hợp rủi ro bộ nhớ/tràn số, trong đó 15 lỗi ẩn) để kiểm chứng khả năng phát hiện của Kripke, Z3 và ASan.</t>
+          <t>Quy trình tiếp nhận và xử lý 1 phiếu nhập kho hàng điện máy gồm 3 hành vi: H1 tiếp nhận thông tin phiếu kho (chép mã phiếu vào bộ đệm stack), H2 tạo danh mục lô hàng (cấp phát mảng động các kiện hàng trên heap), H3 tính toán giá trị tồn kho (phép nhân và cộng dồn số nguyên 32-bit, VND). Bản v0 CÀI LỖI CÓ CHỦ ĐÍCH (12 trường hợp rủi ro bộ nhớ/tràn số) để kiểm chứng khả năng phát hiện của mô hình Kripke, công cụ của Thầy và ASan.</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,24 +525,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mã phiếu kho dài đúng 16 ký tự và 100 ký tự</t>
+          <t>Nhập mã phiếu dài đúng 16 ký tự và 24 ký tự</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>parse_voucher_id (v0: buffer 16, strcpy)</t>
+          <t>doc_ma_phieu (v0: buffer 16, strcpy)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1. Sinh mã C
-2. Chạy check_c_source()
-3. Kiểm tra AG(!buffer_overflow), AG(!off_by_one)</t>
+          <t>1. Chạy tool kiểm chứng mô hình trên JSON v0
+2. Chạy mã C v0 qua ASan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>v0: strcpy gây CWE-120, 2 công thức VI PHẠM; v1: 0 vi phạm, công thức ĐÚNG</t>
+          <t>v0: Vi phạm AG(!buffer_overflow), ASan báo stack-buffer-overflow; v1: 0 lỗi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -564,23 +563,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bản sửa có cắt cụt mã phiếu 16 ký tự không</t>
+          <t>Mã phiếu kho có bị cắt cụt không</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mô hình con M1, luồng M1-v1a vs M1-v1b</t>
+          <t>Kiểm tra độ dài mã phiếu bằng strnlen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1. Nạp M1 vào tab kiểm chứng
-2. Kiểm tra AG(!truncated)</t>
+          <t>1. Nhập mã phiếu chuẩn 12 ký tự
+2. Kiểm tra cờ kết thúc \0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M1-v1a: VI PHẠM (bị cắt mất ký tự); M1-v1b: ĐÚNG hoàn toàn</t>
+          <t>v0: Nguy cơ mất cờ \0; v1: Lưu đủ 12 ký tự kèm \0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -597,29 +596,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REQ-03, REQ-04, REQ-05</t>
+          <t>REQ-03, REQ-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cấp phát mảng kiện hàng trên heap</t>
+          <t>Cấp phát mảng lô hàng và rò rỉ bộ nhớ khi hủy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>create_stock_items; mô hình con M2</t>
+          <t>cap_phat_lo_hang trên heap</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1. Quét mã C
-2. Kiểm tra AG(!null_deref), AG(!alloc_size_overflow)
-3. Chạy KiemTraSoHoc alloc_bytes</t>
+          <t>1. Cấp phát 10 lô hàng
+2. Kích hoạt hủy phiếu không qua free()</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>v0: 3 công thức VI PHẠM, alloc_bytes SAT; v1: 0 vi phạm, UNSAT</t>
+          <t>v0: Vi phạm AG(!memory_leak), ASan báo rò rỉ; v1: Giải phóng sạch 100%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -636,28 +634,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REQ-06, CON-03, CON-04</t>
+          <t>REQ-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tổng tiền nhân và cộng dồn tràn int32</t>
+          <t>Sử dụng con trỏ lô hàng sau khi giải phóng</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KiemTraSoHoc line_amount_mul, accumulated_total</t>
+          <t>truy_cap_lo_hang_sau_free</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. Chạy check_satisfiability() Z3 trên điều kiện
-2. Đưa phản ví dụ vào mã C</t>
+          <t>1. Gọi free(lo_hang)
+2. Đọc lại trường ten_hang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>v0: SAT kèm phản ví dụ (don_gia=30tr, sl=100); v1: UNSAT do có guard</t>
+          <t>v0: Vi phạm AG(!use_after_free), ASan báo crash UAF; v1: Con trỏ gán NULL an toàn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -674,27 +672,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REQ-08, CON-03</t>
+          <t>REQ-06, CON-03, CON-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Số tiền âm do chiết khấu kho vượt tổng</t>
+          <t>Tràn số nguyên phép nhân giá trị lô hàng</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KiemTraSoHoc negative_stock_total</t>
+          <t>KiemTraSoHoc tinh_tien_nhan_lo_hang</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. Chạy check_satisfiability() Z3</t>
+          <t>1. Chạy Z3 SMT Solver tìm nghiệm SAT
+2. Đưa bộ số vào hàm C tính tiền</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>v0: SAT (discount &gt; subtotal); v1: UNSAT</t>
+          <t>v0: Z3 trả về SAT (don_gia=30.000.000, so_luong=100); v1: UNSAT do có kiểm tra biên</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -711,27 +710,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REQ-09, CON-05</t>
+          <t>REQ-07, CON-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tính khấu hao / giá bình quân với kỳ hạn = 0</t>
+          <t>Tràn số nguyên khi cộng dồn tổng kho</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hàm chia calc_unit_price_average(total, months)</t>
+          <t>KiemTraSoHoc tong_tien_cong_don_kho</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. Chạy kiểm thử fuzzing số nguyên</t>
+          <t>1. Chạy Z3 SMT Solver
+2. Cộng dồn vào kho hàng</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>v0: Crash ZeroDivisionError (CWE-369); v1: Kiểm tra months &gt;= 1</t>
+          <t>v0: SAT kèm phản ví dụ; v1: UNSAT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -748,296 +748,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REQ-10, CON-02</t>
+          <t>REQ-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mã token thủ kho dài hơn 32 ký tự</t>
+          <t>Tính đơn giá trung bình khi số lượng bằng 0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>parse_auth_token (v0: buffer 32, strcpy)</t>
+          <t>KiemTraSoHoc chia_cho_khong_don_gia_tb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. Nạp chuỗi 48 byte
-2. Kiểm tra tràn bộ đệm</t>
+          <t>1. Đưa số lượng = 0 vào phép chia
+2. Kiểm tra tín hiệu FPE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>v0: dangerous-function strcpy; v1: 0 vi phạm</t>
+          <t>v0: Báo lỗi chia cho 0; v1: Kiểm tra trước if (tong_sl &gt; 0)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC-08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>REQ-11</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nhánh ẩn backdoor bỏ qua quyền thủ kho</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Hàm stock_debug_bypass(manager_id, pin)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1. Chạy concolic execution trên nhánh điều kiện</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>v0: Tìm ra bộ mã PIN ẩn (CWE-912); v1: Xóa bỏ nhánh debug</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TC-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>REQ-12, NFR-03</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rò rỉ bộ nhớ khi ghi log lỗi kho</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>write_audit_log (v0: malloc không free khi return sớm)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1. Chạy AddressSanitizer (ASan)
-2. Kiểm tra leak report</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>v0: LeakSanitizer báo rò rỉ 32 byte (CWE-401); v1: 0 byte rò rỉ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TC-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>REQ-13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Chuỗi định dạng trong log kiểm kê</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Mô hình con M5; printf(msg)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1. Đưa chuỗi chứa %x%n vào log
-2. Quét lỗ hổng format string</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>v0: VI PHẠM AG(!format_string) (CWE-134); v1: printf("%s", msg) an toàn</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TC-11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>REQ-14, NFR-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Worker nhập và xuất cùng đóng phiên kho</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Trạng thái h6_tranh_chap; LoaiTru nhap_locked, xuat_locked</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1. Mô phỏng 2 thread đồng thời vào phiên kho
-2. Kiểm tra mutex lock</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>v0: Mutual exclusion VI PHẠM (CWE-362); v1: ĐÚNG với mutex</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TC-12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>REQ-15, REQ-16</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Double free và Use-after-free khi đóng phiên</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>close_stock_session, release_voucher_buffer</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1. Gộp mã C thực thi
-2. Chạy với ASan</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>v0: ASan bắt double-free (CWE-415) và heap-use-after-free (CWE-416); v1: 0 lỗi</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TC-13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>REQ-17, NFR-05</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mã PIN két kho còn sót trong RAM sau khi free</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mô hình con M6; con_ma_pin</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1. Kiểm tra AG(!secret_residue)
-2. Kiểm tra vùng nhớ sau free()</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>v0: VI PHẠM (CWE-226/244); v1: explicit_bzero trước free an toàn</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TC-14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>REQ-18</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Kiểm chứng toàn luồng phiếu kho</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Mô hình 36 trạng thái (sheet MoHinhTrangThai)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1. Chạy kiểm chứng Kripke trên toàn bộ 22 công thức CTL
-2. Kiểm tra deadlock</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Không deadlock; v0: 16 công thức VI PHẠM; v1: 100% công thức ĐÚNG</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1054,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1087,7 +822,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H1: Hàm đọc mã phiếu kho (parse_voucher_id) không được ghi vượt biên bộ đệm, kể cả khi mã dài ĐÚNG 16 ký tự (C1.2, C1.3)</t>
+          <t>H1: Hàm đọc mã phiếu kho (doc_ma_phieu) không được ghi vượt biên bộ đệm 16 byte, kể cả khi mã dài ĐÚNG 16 ký tự</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1109,7 +844,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1: Mã phiếu hợp lệ không được bị cắt cụt hoặc biến đổi khi lưu vào bộ đệm stack (C1.4)</t>
+          <t>H1: Mã phiếu hợp lệ không được bị cắt cụt hoặc biến đổi khi lưu vào bộ đệm stack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1131,7 +866,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H2: Kết quả cấp phát mảng sản phẩm lô hàng (create_stock_items) phải được kiểm tra NULL trước khi sử dụng (C2.2)</t>
+          <t>H2: Kết quả cấp phát mảng lô hàng (cap_phat_lo_hang) phải được kiểm tra con trỏ NULL trước khi sử dụng</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1153,12 +888,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2: Kích thước vùng nhớ cấp phát heap (số kiện x kích thước 1 kiện) không được tràn số hoặc âm (C2.3)</t>
+          <t>H2: Bộ nhớ cấp phát cho danh mục lô hàng phải được giải phóng hoàn toàn khi hủy phiếu hoặc hoàn tất đơn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1175,7 +910,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2: Các trường dữ liệu của từng kiện hàng mới cấp phát phải được khởi tạo đầy đủ trước khi đọc (C2.4)</t>
+          <t>H2: Con trỏ lô hàng không được phép truy cập sau khi đã gọi free (chống Use-After-Free) và không được free 2 lần</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1197,7 +932,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3: Phép tính giá trị từng dòng lô hàng (line_total = don_gia * so_luong) không được tràn số nguyên 32-bit (C3.2)</t>
+          <t>H3: Phép tính giá trị từng dòng lô hàng (đơn giá x số lượng) không được tràn số nguyên 32-bit có dấu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,7 +954,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3: Phép cộng dồn tổng giá trị kho hàng không được vượt trần int32 (tối đa 2.147.483.647 VND) (C3.3)</t>
+          <t>H3: Phép cộng dồn tổng giá trị kho hàng không được vượt trần int32 (tối đa 2.147.483.647 VND)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1241,7 +976,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3: Số tiền sau khi trừ chiết khấu kho không được âm (C3.4)</t>
+          <t>H3: Số lượng hàng hóa nhập kho phải là số nguyên dương; đơn giá bình quân không được chia cho 0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1250,226 +985,6 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REQ-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>H3: Đơn giá bình quân mặt hàng không được chia cho số lượng bằng 0 (C3.5)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>arithmetic</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REQ-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>H4: Hàm đọc token xác thực thủ kho (parse_auth_token) không được ghi vượt bộ đệm 32 byte (C4.2)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REQ-11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>H4: Không được có nhánh ẩn (backdoor/debug pin) bỏ qua kiểm tra quyền xuất kho khẩn cấp (C4.3)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>safety</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REQ-12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H5: Vùng nhớ buffer ghi nhật ký kiểm kê (write_audit_log) phải được giải phóng sạch khi gặp lỗi thoát sớm (C5.2)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REQ-13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>H5: Thông điệp log từ người dùng nhập không được đưa trực tiếp vào định dạng printf mà phải dùng printf("%s", msg) (C5.3)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>safety</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REQ-14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H6: Hai worker (nhập kho và xuất kho tự động) không được truy cập đồng thời vào phiên kho chưa khóa mutex (C6.2)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>concurrency</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REQ-15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H6: Không được giải phóng hai lần (double free) trên cùng một con trỏ danh mục lô hàng (C6.3)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REQ-16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>H6: Không được đọc/ghi vào con trỏ lô hàng sau khi đã giải phóng (use-after-free) (C6.4)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REQ-17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>H6: Mã PIN két thủ kho lưu tạm trong bộ nhớ phải được xóa sạch (zero-out) trước khi free (C6.5)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REQ-18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Toàn bộ luồng phiếu kho: Luôn kết thúc hợp lệ và tồn tại nhánh từ chối đầu vào độc hại</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>liveness</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1486,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1514,7 +1029,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hệ thống xử lý tối thiểu 200 giao dịch kiểm kê/giây trên phần cứng tham chiếu</t>
+          <t>Hệ thống phản hồi thao tác quét mã và tính toán trong tối đa 1.0 giây</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1531,7 +1046,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phản hồi xác thực quyền thủ kho trong tối đa 2 giây</t>
+          <t>Bộ nhớ RAM tiến trình không tăng dần theo thời gian (0 byte rò rỉ bộ nhớ sau khi xử lý phiếu)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1548,44 +1063,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bộ nhớ RAM tiến trình không tăng quá 5% sau 1.000.000 lần tạo/hủy phiếu kho (0 byte rò rỉ)</t>
+          <t>Bản vá v1 phải vượt qua 100% kiểm tra của AddressSanitizer (ASan) và Z3 SMT Solver</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NFR-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Phiên kho tự hết hạn sau 15 phút nếu thủ kho không xác nhận (timeout guard)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NFR-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Dữ liệu mã PIN thủ kho và khóa bảo mật bị xóa ngay lập tức khỏi RAM sau khi hoàn tất</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1602,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,7 +1111,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mã phiếu kho tối đa 16 ký tự ASCII (cần 17 byte bộ đệm để chứa cả ký tự null \0)</t>
+          <t>Mã phiếu kho tối đa 16 ký tự ASCII (cần 17 byte bộ đệm để chứa ký tự null \0)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1647,7 +1128,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mã token xác thực thủ kho tối đa 32 ký tự ASCII</t>
+          <t>Mỗi phiếu kho có từ 1 đến 500 kiện hàng; mỗi kiện có số lượng 1–1000 chiếc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1664,7 +1145,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mỗi phiếu kho có 1–500 kiện hàng; số lượng mỗi kiện 1–1000 chiếc; đơn giá 0–50.000.000 VND</t>
+          <t>Đơn giá thiết bị điện máy từ 0 đến 50.000.000 VND/chiếc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1681,61 +1162,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Số tiền tính bằng VND; bản v0 dùng int 32-bit có dấu (tối đa 2.147.483.647); hạn mức 1 phiếu kho là 2.000.000.000 VND</t>
+          <t>Số tiền tính bằng VND sử dụng kiểu int32 có dấu (giới hạn tối đa 2.147.483.647 VND)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CON-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kỳ hạn kiểm kê khấu hao từ 1 đến 36 tháng; không cho phép kỳ hạn = 0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CON-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chuỗi nhật ký kiểm kê tối đa 256 ký tự</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CON-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mã PIN bảo mật két kho gồm đúng 6 chữ số</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1752,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,7 +1245,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bắt đầu xử lý 1 phiếu kho</t>
+          <t>Bắt đầu xử lý 1 phiếu nhập kho</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1273,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nhận chuỗi mã phiếu từ client</t>
+          <t>Nhận chuỗi mã phiếu từ bàn phím/máy quét</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1357,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mã 100 ký tự: tràn bộ đệm stack đè return address</t>
+          <t>Mã dài 24 ký tự: tràn bộ đệm stack ghi đè địa chỉ trở về</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1375,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>h2_ok, h2_null, h2_sai_kich_thuoc, h2_doc_rac</t>
+          <t>h2_ok, h2_null, h2_ro_ri_heap, h2_uaf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1955,7 +1385,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cấp phát mảng kiện hàng trên heap</t>
+          <t>Cấp phát mảng lô hàng trên heap bằng malloc</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1398,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h2, allocated, initialized</t>
+          <t>h2, alloc_ok</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1983,7 +1413,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cấp phát và khởi tạo an toàn</t>
+          <t>Cấp phát heap thành công và quản lý con trỏ an toàn</t>
         </is>
       </c>
     </row>
@@ -2011,20 +1441,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>malloc trả về NULL không kiểm tra</t>
+          <t>Không kiểm tra NULL sau malloc, gây crash khi cạn RAM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>h2_sai_kich_thuoc</t>
+          <t>h2_ro_ri_heap</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h2, alloc_size_overflow, heap_overflow, violation</t>
+          <t>h2, memory_leak, violation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2039,20 +1469,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kích thước cấp phát tràn khi số lượng n không giới hạn</t>
+          <t>Hủy phiếu kho đột ngột mà quên free(), gây rò rỉ bộ nhớ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>h2_doc_rac</t>
+          <t>h2_uaf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h2, uninit_read, violation</t>
+          <t>h2, use_after_free, violation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2067,7 +1497,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Đọc kiện hàng chưa khởi tạo dữ liệu</t>
+          <t>Truy cập in phiếu sau khi đã giải phóng con trỏ lô hàng</t>
         </is>
       </c>
     </row>
@@ -2080,12 +1510,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h3, computing</t>
+          <t>h3, calculating</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>h3_ok, h3_tran_so, h3_so_am, h3_chia_0</t>
+          <t>h3_ok, h3_tran_nhan, h3_tran_cong, h3_chia_0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2095,7 +1525,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tính tiền từng lô hàng và cộng dồn tổng kho</t>
+          <t>Tính tiền từng mặt hàng và cộng dồn tổng kho</t>
         </is>
       </c>
     </row>
@@ -2108,12 +1538,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h3, amount_ok</t>
+          <t>h3, math_ok</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>h4_vao</t>
+          <t>ket_thuc_an_toan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2123,20 +1553,20 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tính toán số học chính xác</t>
+          <t>Tính toán số học chính xác, không tràn số</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>h3_tran_so</t>
+          <t>h3_tran_nhan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h3, int_overflow, violation</t>
+          <t>h3, integer_overflow, violation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2146,25 +1576,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C3.2/C3.3</t>
+          <t>C3.2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Phép nhân đơn giá x số lượng hoặc cộng dồn vượt trần int32</t>
+          <t>Đơn giá x số lượng &gt; 2.147.483.647 VND làm tiền bị âm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>h3_so_am</t>
+          <t>h3_tran_cong</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h3, negative_amount, violation</t>
+          <t>h3, integer_overflow, violation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2174,12 +1604,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C3.4</t>
+          <t>C3.3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chiết khấu lớn hơn tổng tiền làm giá trị bị âm</t>
+          <t>Cộng dồn các kiện hàng vượt quá hạn mức trần int32</t>
         </is>
       </c>
     </row>
@@ -2202,572 +1632,68 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C3.5</t>
+          <t>C3.4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tính đơn giá bình quân khi số lượng kiện bằng 0</t>
+          <t>Tính đơn giá trung bình khi số lượng = 0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>h4_vao</t>
+          <t>ket_thuc_an_toan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h4, token_received</t>
+          <t>flow_end, safe, completed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>h4_ok, h4_tu_choi_quyen, h4_tran_token, h4_nhanh_an</t>
+          <t>ket_thuc_an_toan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>END_OK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Xác thực token ủy quyền thủ kho</t>
+          <t>Hoàn tất quy trình phiếu kho an toàn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>h4_ok</t>
+          <t>dung_khong_an_toan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h4, token_verified</t>
+          <t>unsafe_halt, violation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>h5_vao</t>
+          <t>dung_khong_an_toan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C4.1</t>
+          <t>END_BAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Xác thực thủ kho thành công</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>h4_tu_choi_quyen</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>h4, token_rejected</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>h6_phien_ranh</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>C4.1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Token không hợp lệ, từ chối an toàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>h4_tran_token</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>h4, buffer_overflow, violation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>C4.2</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Token dài hơn 32 byte gây tràn bộ đệm</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>h4_nhanh_an</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>h4, hidden_bypass, violation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>C4.3</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Nhánh ẩn backdoor bỏ qua xác thực thủ kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>h5_vao</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>h5, logging</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>h5_ok, h5_ro_ri, h5_format_string</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ghi nhật ký kiểm kê kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>h5_ok</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h5, log_freed</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>h6_phien_ranh</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>C5.1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ghi log an toàn và giải phóng buffer</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>h5_ro_ri</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h5, mem_leak, violation</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>C5.2</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Return sớm khi lỗi mà quên giải phóng buffer log</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>h5_format_string</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h5, format_string, violation</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>C5.3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Đưa chuỗi log trực tiếp vào printf(msg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>h6_phien_ranh</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h6, sess_free</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>h6_nhap_giu, h6_xuat_giu</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>H6</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Phiên kho ở trạng thái rảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>h6_nhap_giu</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h6, nhap_locked</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>h6_giai_phong, h6_tranh_chap</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>C6.1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Worker nhập kho giữ khóa phiên</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>h6_xuat_giu</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h6, xuat_locked</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>h6_giai_phong, h6_tranh_chap</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>C6.1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Worker xuất kho giữ khóa phiên</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>h6_tranh_chap</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>h6, nhap_locked, xuat_locked, race, violation</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>h6_double_free, h6_uaf</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>C6.2</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hai worker đồng thời thao tác phiên kho không khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>h6_double_free</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>h6, double_free, violation</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>C6.3</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Cả 2 worker cùng gọi free() trên con trỏ lô hàng</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>h6_uaf</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>h6, use_after_free, violation</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>C6.4</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Worker xuất kho đọc dữ liệu sau khi worker nhập đã free</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>h6_giai_phong</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>h6, releasing</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ket_thuc_ok, h6_con_ma_pin</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>C6.1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Giải phóng tài nguyên phiên kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>h6_con_ma_pin</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h6, secret_residue, violation</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>C6.5</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Mã PIN két kho còn sót trên RAM sau khi free</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ket_thuc_ok</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>flow_end, stock_done, mem_clean</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ket_thuc_ok</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Hoàn tất giao dịch kho an toàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ket_thuc_tu_choi</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>flow_end, input_rejected, mem_clean</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ket_thuc_tu_choi</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Từ chối đầu vào không hợp lệ an toàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>unsafe_halt</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Dừng hệ thống do phát hiện lỗi bộ nhớ</t>
+          <t>Dừng khẩn cấp do phát hiện lỗi bộ nhớ hoặc tràn số</t>
         </is>
       </c>
     </row>
@@ -2782,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2805,7 +1731,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Safety tổng quát: không bao giờ rơi vào bất kỳ trạng thái vi phạm nào</t>
+          <t>Safety tổng quát: Không bao giờ rơi vào trạng thái vi phạm</t>
         </is>
       </c>
     </row>
@@ -2817,7 +1743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safety C1.2, C1.3, C4.2 — CWE-120/787 (Tràn bộ đệm stack)</t>
+          <t>Safety H1: Chống tràn bộ đệm stack (CWE-120/121)</t>
         </is>
       </c>
     </row>
@@ -2829,7 +1755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Safety C1.2 — CWE-193 (Tràn 1 byte null terminator)</t>
+          <t>Safety H1: Chống lỗi tràn 1 byte null terminator (CWE-193)</t>
         </is>
       </c>
     </row>
@@ -2841,223 +1767,79 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Safety C2.2 — CWE-476 (Giải tham chiếu con trỏ NULL)</t>
+          <t>Safety H2: Chống giải tham chiếu con trỏ NULL (CWE-476)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AG(!alloc_size_overflow)</t>
+          <t>AG(!memory_leak)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Safety C2.3 — CWE-122 (Tràn kích thước cấp phát heap)</t>
+          <t>Safety H2: Chống rò rỉ bộ nhớ Heap khi kết thúc/hủy (CWE-401)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AG(!uninit_read)</t>
+          <t>AG(!use_after_free)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Safety C2.4 — CWE-457 (Đọc bộ nhớ chưa khởi tạo)</t>
+          <t>Safety H2: Chống sử dụng con trỏ sau khi giải phóng (CWE-416)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AG(!int_overflow)</t>
+          <t>AG(!integer_overflow)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Safety C3.2, C3.3 — CWE-190 (Tràn số nguyên 32-bit có dấu)</t>
+          <t>Safety H3: Chống tràn số nguyên có dấu 32-bit (CWE-190)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AG(!negative_amount)</t>
+          <t>AG(!div_by_zero)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Safety C3.4 — CWE-191 (Số tiền âm sau chiết khấu)</t>
+          <t>Safety H3: Chống lỗi chia cho 0 khi tính trung bình (CWE-369)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AG(!div_by_zero)</t>
+          <t>AF(flow_end)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Safety C3.5 — CWE-369 (Chia cho 0 khi tính đơn giá TB)</t>
+          <t>Liveness: Mọi luồng xử lý cuối cùng đều phải về trạng thái kết thúc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AG(!hidden_bypass)</t>
+          <t>EF(ket_thuc_an_toan)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Safety C4.3 — CWE-912 (Nhánh ẩn vượt quyền thủ kho)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AG(!mem_leak)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Safety C5.2 — CWE-401 (Rò rỉ bộ nhớ heap khi ghi log)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AG(!format_string)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Safety C5.3 — CWE-134 (Lỗ hổng format string trong log)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AG(!race)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Safety C6.2 — CWE-362 (Tranh chấp đồng thời trên phiên kho)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AG(!double_free)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Safety C6.3 — CWE-415 (Giải phóng vùng nhớ hai lần)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AG(!use_after_free)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Safety C6.4 — CWE-416 (Truy cập con trỏ sau khi free)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AG(!secret_residue)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Safety C6.5 — CWE-226/244 (Mã PIN bảo mật còn sót lại trên RAM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AF(flow_end)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Liveness REQ-18: mọi luồng xử lý cuối cùng đều kết thúc hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EF(stock_done)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Reachability: Luồng xử lý kho hoàn tất thành công tồn tại</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>EF(input_rejected)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Reachability: Tồn tại nhánh từ chối đầu vào độc hại an toàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>EG(!violation)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tồn tại ít nhất 1 đường đi luôn an toàn tuyệt đối</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EF(nhap_locked)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Khả đạt của cụm khóa phiên nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>EF(xuat_locked)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Khả đạt của cụm khóa phiên xuất kho</t>
+          <t>Reachability: Tồn tại ít nhất một kịch bản hoàn tất an toàn</t>
         </is>
       </c>
     </row>
@@ -3072,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3090,72 +1872,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nhap_locked</t>
+          <t>violation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>xuat_locked</t>
+          <t>flow_end</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>violation</t>
+          <t>unsafe_halt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flow_end</t>
+          <t>safe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stock_done</t>
+          <t>use_after_free</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>input_rejected</t>
+          <t>alloc_ok</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unsafe_halt</t>
+          <t>memory_leak</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mem_clean</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>use_after_free</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mem_clean</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>secret_residue</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mem_clean</t>
+          <t>safe</t>
         </is>
       </c>
     </row>
@@ -3170,7 +1928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3208,7 +1966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parse_voucher_id</t>
+          <t>doc_ma_phieu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3223,7 +1981,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>raw_voucher_id</t>
+          <t>chuoi_dau_vao</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3240,7 +1998,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>parse_auth_token</t>
+          <t>cap_phat_lo_hang</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3250,29 +2008,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>buffer_copy</t>
+          <t>alloc_release</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>raw_token</t>
+          <t>so_luong_lo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>buffer-overflow</t>
+          <t>memory-leak</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>create_stock_items</t>
+          <t>truy_cap_lo_hang_sau_free</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3285,18 +2043,26 @@
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>con_tro_lo</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>use-after-free</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>write_audit_log</t>
+          <t>tinh_tien_lo_hang</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3306,172 +2072,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alloc_release</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>don_gia, so_luong</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>memory-leak</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>close_stock_session</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>alloc_release</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>double-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>release_voucher_buffer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>alloc_release</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>use-after-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>calc_line_amount</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>arithmetic</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>don_gia, so_luong</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>accumulate_stock_value</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>arithmetic</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>total_before, line_total</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>calc_unit_price_average</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>divide</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>total, n_items</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>stock_debug_bypass</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>magic_value</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>manager_id, debug_pin</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>integer-overflow</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3484,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3517,162 +2135,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>line_amount_mul</t>
+          <t>tinh_tien_nhan_lo_hang</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>price, qty</t>
+          <t>don_gia, so_luong</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>price &gt;= 0 and price &lt;= 50000000 and qty &gt;= 1 and qty &lt;= 1000 and price * qty &gt; 2147483647</t>
+          <t>don_gia &gt;= 0 and don_gia &lt;= 50000000 and so_luong &gt;= 1 and so_luong &lt;= 1000 and don_gia * so_luong &gt; 2147483647</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>price * qty</t>
+          <t>don_gia * so_luong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C3.2 — Phép nhân đơn giá x số lượng kiện tràn int32</t>
+          <t>Phép nhân đơn giá x số lượng vượt trần int32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>accumulated_total</t>
+          <t>tong_tien_cong_don_kho</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>total_before, line_total</t>
+          <t>tong_truoc, tien_lo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>total_before &gt;= 0 and total_before &lt;= 2147483647 and line_total &gt;= 0 and line_total &lt;= 50000000 and total_before + line_total &gt; 2147483647</t>
+          <t>tong_truoc &gt;= 0 and tong_truoc &lt;= 2147483647 and tien_lo &gt;= 0 and tien_lo &lt;= 50000000 and tong_truoc + tien_lo &gt; 2147483647</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>total_before + line_total</t>
+          <t>tong_truoc + tien_lo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C3.3 — Cộng dồn các kiện hàng làm tổng giá trị vượt trần</t>
+          <t>Cộng dồn giá trị các kiện hàng làm tràn số tiền tổng</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>voucher_total_int32</t>
+          <t>chia_cho_khong_don_gia_tb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>subtotal, packing_fee</t>
+          <t>tong_tien, tong_sl</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>subtotal &gt;= 0 and subtotal &lt;= 2147483647 and packing_fee &gt;= 0 and packing_fee &lt;= 500000 and subtotal + packing_fee &gt; 2147483647</t>
+          <t>tong_tien &gt;= 0 and tong_sl == 0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>subtotal + packing_fee</t>
+          <t>tong_tien / tong_sl</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C3.2 — Cộng phí đóng gói bảo quản vào tiền hàng gần trần</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>alloc_bytes</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>n_items, item_size</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>n_items &gt;= 1 and item_size == 48 and n_items * item_size &gt; 2147483647</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>n_items * item_size</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C2.3 — Kích thước cấp phát heap tràn khi n không bị giới hạn</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>negative_stock_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>subtotal, discount</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>subtotal &gt;= 0 and subtotal &lt;= 2000000000 and discount + 2000000000 &gt;= 0 and discount &lt;= 2000000000 and subtotal - discount &lt; 0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>subtotal - discount</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>C3.4 — Chiết khấu kho hàng lớn hơn tổng tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>div_by_zero_avg</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>total_amount, total_items</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>total_amount &gt;= 0 and total_items == 0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>total_amount / total_items</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>C3.5 — Chia cho 0 khi tính đơn giá bình quân</t>
+          <t>Lỗi chia cho 0 khi tính đơn giá trung bình</t>
         </is>
       </c>
     </row>
